--- a/data/gravel/Genesis Vagabond 2025.xlsx
+++ b/data/gravel/Genesis Vagabond 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4EE19D-79DA-AA46-A61E-AAFE8CA6C440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB7326E-BA0F-534C-B82B-8F65FBBA5C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23280" yWindow="-20200" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -327,6 +327,24 @@
   </si>
   <si>
     <t>a8:g33</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -679,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1268,10 +1286,10 @@
     </row>
     <row r="36" spans="1:7" ht="21">
       <c r="A36" t="s">
-        <v>31</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
+      </c>
+      <c r="B36" t="s">
+        <v>99</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
@@ -1280,9 +1298,11 @@
     </row>
     <row r="37" spans="1:7" ht="21">
       <c r="A37" t="s">
-        <v>32</v>
-      </c>
-      <c r="B37" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="B37" t="s">
+        <v>101</v>
+      </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -1290,52 +1310,56 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>102</v>
+      </c>
+      <c r="B38" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39">
-        <v>60</v>
+        <v>31</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B40" s="1"/>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41" s="1">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>34</v>
+      </c>
+      <c r="B42">
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>38</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B43" s="1"/>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="B44" s="1">
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>95</v>
@@ -1343,10 +1367,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>96</v>
@@ -1354,166 +1375,187 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>40</v>
+      </c>
+      <c r="B48">
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B49">
-        <v>31.6</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>47</v>
-      </c>
-      <c r="B52" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="B52">
+        <v>31.6</v>
+      </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>48</v>
-      </c>
-      <c r="B53">
-        <v>180</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B53" s="1"/>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>49</v>
-      </c>
-      <c r="B54">
-        <v>160</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>50</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B55" s="1"/>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>48</v>
+      </c>
+      <c r="B56">
+        <v>180</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>52</v>
-      </c>
-      <c r="B57" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="B57">
+        <v>160</v>
+      </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>55</v>
-      </c>
-      <c r="B60">
-        <v>2</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B60" s="1"/>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62" s="1">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>58</v>
-      </c>
-      <c r="B63" s="1">
-        <v>3</v>
+        <v>55</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>59</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>69</v>
+        <v>56</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>60</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>69</v>
+        <v>57</v>
+      </c>
+      <c r="B65" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>61</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>69</v>
+        <v>58</v>
+      </c>
+      <c r="B66" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>62</v>
-      </c>
-      <c r="B67">
-        <v>899</v>
+        <v>59</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>63</v>
-      </c>
-      <c r="B68">
-        <v>1799</v>
+        <v>60</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>64</v>
+        <v>61</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
+        <v>62</v>
+      </c>
+      <c r="B70">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>63</v>
+      </c>
+      <c r="B71">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
         <v>65</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>94</v>
       </c>
     </row>

--- a/data/gravel/Genesis Vagabond 2025.xlsx
+++ b/data/gravel/Genesis Vagabond 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB7326E-BA0F-534C-B82B-8F65FBBA5C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2869EE5F-7ED6-F649-82D8-56EB4D165E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -317,9 +317,6 @@
     <t>threaded</t>
   </si>
   <si>
-    <t>pounds</t>
-  </si>
-  <si>
     <t>mtb</t>
   </si>
   <si>
@@ -345,6 +342,9 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>GBP</t>
   </si>
 </sst>
 </file>
@@ -748,7 +748,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="21">
@@ -1286,10 +1286,10 @@
     </row>
     <row r="36" spans="1:7" ht="21">
       <c r="A36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" t="s">
         <v>98</v>
-      </c>
-      <c r="B36" t="s">
-        <v>99</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="37" spans="1:7" ht="21">
       <c r="A37" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" t="s">
         <v>100</v>
-      </c>
-      <c r="B37" t="s">
-        <v>101</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
@@ -1310,10 +1310,10 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" t="s">
         <v>102</v>
-      </c>
-      <c r="B38" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1362,7 +1362,7 @@
         <v>37</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1370,7 +1370,7 @@
         <v>38</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1556,7 +1556,7 @@
         <v>65</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Genesis Vagabond 2025.xlsx
+++ b/data/gravel/Genesis Vagabond 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2869EE5F-7ED6-F649-82D8-56EB4D165E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D66FD3F-109B-844A-A461-B7B6C916C64B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -305,9 +305,6 @@
     <t>Stem Length</t>
   </si>
   <si>
-    <t>https://www.genesisbikes.co.uk/product/genesis-vagabond-frameset-vargn12010/VARGN12010/GN12010LG</t>
-  </si>
-  <si>
     <t>effective_reach</t>
   </si>
   <si>
@@ -345,6 +342,12 @@
   </si>
   <si>
     <t>GBP</t>
+  </si>
+  <si>
+    <t>https://www.genesisbikes.co.uk/products?categories=the-bikes~vagabond</t>
+  </si>
+  <si>
+    <t>https://www.freewheel.co.uk/media/catalog/product/cache/0856fa1c78c25ad1f0603c35c65b3119/f/t/ftp_f_freewheel_imagessportlinefwbikesgn11910_detail_01.jpg</t>
   </si>
 </sst>
 </file>
@@ -740,7 +743,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="B6" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -748,7 +756,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="21">
@@ -776,7 +784,7 @@
     </row>
     <row r="9" spans="1:7" ht="21">
       <c r="A9" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>79</v>
@@ -1286,10 +1294,10 @@
     </row>
     <row r="36" spans="1:7" ht="21">
       <c r="A36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" t="s">
         <v>97</v>
-      </c>
-      <c r="B36" t="s">
-        <v>98</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
@@ -1298,10 +1306,10 @@
     </row>
     <row r="37" spans="1:7" ht="21">
       <c r="A37" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" t="s">
         <v>99</v>
-      </c>
-      <c r="B37" t="s">
-        <v>100</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
@@ -1310,10 +1318,10 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" t="s">
         <v>101</v>
-      </c>
-      <c r="B38" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1321,7 +1329,7 @@
         <v>31</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1362,7 +1370,7 @@
         <v>37</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1370,7 +1378,7 @@
         <v>38</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1399,7 +1407,7 @@
         <v>42</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1556,7 +1564,7 @@
         <v>65</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Genesis Vagabond 2025.xlsx
+++ b/data/gravel/Genesis Vagabond 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D66FD3F-109B-844A-A461-B7B6C916C64B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1842DF1D-8ED3-8A4F-A2A3-6E8F619E69A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,12 @@
   </si>
   <si>
     <t>https://www.freewheel.co.uk/media/catalog/product/cache/0856fa1c78c25ad1f0603c35c65b3119/f/t/ftp_f_freewheel_imagessportlinefwbikesgn11910_detail_01.jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Milton Keynes, United Kingdom</t>
   </si>
 </sst>
 </file>
@@ -700,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1567,6 +1573,14 @@
         <v>102</v>
       </c>
     </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>105</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Genesis Vagabond 2025.xlsx
+++ b/data/gravel/Genesis Vagabond 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1842DF1D-8ED3-8A4F-A2A3-6E8F619E69A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B16A95-17AD-6E45-B2C6-EA638E7422CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>Milton Keynes, United Kingdom</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -1476,7 +1479,9 @@
       <c r="A60" t="s">
         <v>52</v>
       </c>
-      <c r="B60" s="1"/>
+      <c r="B60" s="1" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">

--- a/data/gravel/Genesis Vagabond 2025.xlsx
+++ b/data/gravel/Genesis Vagabond 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B16A95-17AD-6E45-B2C6-EA638E7422CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CF4BDA-F43C-534D-994B-E29584D7E986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -357,6 +357,24 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -709,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1413,176 +1431,206 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52">
-        <v>31.6</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="1"/>
+        <v>111</v>
+      </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>47</v>
-      </c>
-      <c r="B55" s="1"/>
+        <v>113</v>
+      </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>48</v>
-      </c>
-      <c r="B56">
-        <v>180</v>
+        <v>42</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>49</v>
-      </c>
-      <c r="B57">
-        <v>160</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B58">
+        <v>31.6</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>51</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B59" s="1"/>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>52</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>53</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B61" s="1"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B62">
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>56</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>57</v>
-      </c>
-      <c r="B65" s="1">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>58</v>
-      </c>
-      <c r="B66" s="1">
-        <v>3</v>
+        <v>52</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>60</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B70">
-        <v>899</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>63</v>
-      </c>
-      <c r="B71">
-        <v>1799</v>
+        <v>57</v>
+      </c>
+      <c r="B71" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="B72" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
+        <v>60</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
         <v>105</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>106</v>
       </c>
     </row>
